--- a/xianyu/ledger.xlsx
+++ b/xianyu/ledger.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet name="闲鱼台账" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'闲鱼台账'!$A$1:$J$4</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="¥#,##0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,34 +31,51 @@
     <font>
       <name val="PingFang SC"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <color rgb="006E7781"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="PingFang SC"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
+      <color rgb="006E7781"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="001F2328"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="005C6470"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="00B07A00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="000969DA"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="001F2328"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="PingFang SC"/>
       <b val="1"/>
       <color rgb="001A7A45"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="PingFang SC"/>
-      <b val="1"/>
-      <color rgb="00555555"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="PingFang SC"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -69,26 +84,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001C3557"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4F7FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EEEEEE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF6"/>
+        <fgColor rgb="00F6F8FA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -97,79 +97,69 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00D0D8E4"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D0D8E4"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D8E4"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color rgb="00D0D8E4"/>
       </bottom>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="001C3557"/>
-      </left>
-      <right style="thin">
-        <color rgb="001C3557"/>
-      </right>
-      <top style="thin">
-        <color rgb="001C3557"/>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="00D0D8E4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="001C3557"/>
-      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -537,35 +527,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="25.5" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>出发日</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>行程</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>商品</t>
+          <t>人</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -595,7 +585,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>关联PNR</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -604,146 +594,238 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>[机票] 东京 HND → 宫古岛 MMY · 单</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>涯石街活跃的花椒12</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>5350</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>7170</v>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>已报价</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="9" t="inlineStr"/>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>[铁路] 京都 → 东京</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>漂洋过海的洋洋</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>已付款</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>[图]</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>买家提供的车次截图：Hikari 644，京都 09:33 → 东京 12:12，2h39m，途径 米原/岐阜羽岛/名古屋/豊桥/新横浜/品川/东京；买家不要富士山位（曾砍价 400 被拒，曾问 420+富士山未接受）；5/2 出票，出票后联系买家发回执</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>[铁路] 东京 → 长野</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>土星务实的奶酪</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>381.46</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>已报价</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>[铁路] 东京站 → 京都站</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>wwwww壹壹</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>已付款</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>取票方式：二维码；出票时间：出发前 2 天（约 5/2）；买家说时间可灵活：「你说啥时候出发就啥时候出发」，但默认 10:00 左右；5/8 京都→关西机场线买家咨询过，已拒（让她自己 Klook 买）；原 JSON 报价 450 错误，与实际聊天 420 不符，已修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>huajiao12_2026-05-04_tyo-mmy</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>东京-宫古岛 单程 1成人+1儿童</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>涯石街活跃的花椒12</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>5350</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>7170</v>
-      </c>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>已报价</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="7" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>[机票] 香港 HKG → 台北桃园 TPE · 往</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>ydedc</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>已预订，待买家确认收货</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>FGC4XU</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>客户询问线上值机，已告知需要去机场值机；客户表示已飞首程，回程拿到登机牌后确认收货</t>
+        </is>
+      </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>wwwwwyiyi_2026-05-04_tokyo-kyoto_rail</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>新干线代订</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>wwwww壹壹</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="F3" s="10" t="n">
-        <v>617</v>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>已报价</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr"/>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>ydedc_2026-04-26_hkg-tpe</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>机票代订</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>ydedc</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>2012</v>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>已预订，待买家确认收货</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>FGC4XU</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>客户询问线上值机，已告知需要去机场值机；客户表示已飞首程，回程拿到登机牌后确认收货</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>共 3 笔</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr"/>
-      <c r="C5" s="12" t="inlineStr"/>
-      <c r="D5" s="12" t="inlineStr"/>
-      <c r="E5" s="13" t="n">
-        <v>7000</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>9799</v>
-      </c>
-      <c r="G5" s="14" t="n">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>共 5 笔</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr"/>
+      <c r="C7" s="13" t="inlineStr"/>
+      <c r="D7" s="13" t="inlineStr"/>
+      <c r="E7" s="14" t="n">
+        <v>7670</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>9563.459999999999</v>
+      </c>
+      <c r="G7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="12" t="inlineStr"/>
-      <c r="J5" s="12" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>